--- a/docs/技術選定・構成検討テンプレート（汎用）.xlsx
+++ b/docs/技術選定・構成検討テンプレート（汎用）.xlsx
@@ -10,27 +10,29 @@
     <sheet sheetId="4" name="STEP1_要件整理" state="visible" r:id="rId7"/>
     <sheet sheetId="5" name="STEP2_技術選定" state="visible" r:id="rId8"/>
     <sheet sheetId="6" name="STEP3_構成設計" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="STEP4_テスト戦略" state="visible" r:id="rId10"/>
-    <sheet sheetId="8" name="STEP5_着手前チェック" state="visible" r:id="rId11"/>
+    <sheet sheetId="7" name="STEP4_設計書作成" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="STEP5_本番リリース・インフラ構成" state="visible" r:id="rId11"/>
+    <sheet sheetId="9" name="STEP6_テスト戦略" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="STEP7_着手前チェック" state="visible" r:id="rId13"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="209">
   <si>
     <t xml:space="preserve">Spring Bootプロジェクト
 技術選定・構成検討テンプレート</t>
   </si>
   <si>
-    <t>～何から考えるべきかを、STEPに分けて整理する～</t>
+    <t>～要件整理から設計書・本番リリースまで、何から考えるべきかをSTEPに分けて整理する～</t>
   </si>
   <si>
     <t>対象</t>
   </si>
   <si>
-    <t>Java／Spring Bootで業務システムを一から作る場合の検討テンプレート</t>
+    <t>Java／Spring Bootで業務システムを一から作る場合の検討テンプレート（設計書作成・本番リリース・バッチ処理を含む）</t>
   </si>
   <si>
     <t>作成日</t>
@@ -87,7 +89,7 @@
     <t>全体像</t>
   </si>
   <si>
-    <t>検討の流れ（STEP1〜5）を1枚で俯瞰する</t>
+    <t>検討の流れ（STEP1〜7）を1枚で俯瞰する</t>
   </si>
   <si>
     <t>4</t>
@@ -105,7 +107,7 @@
     <t>STEP2_技術選定</t>
   </si>
   <si>
-    <t>何を使うか決める</t>
+    <t>何を使うか決める（言語・DB・画面・JS/CSS・IDE・開発手法）</t>
   </si>
   <si>
     <t>6</t>
@@ -114,31 +116,49 @@
     <t>STEP3_構成設計</t>
   </si>
   <si>
-    <t>どう組み立てるか決める</t>
+    <t>どう組み立てるか決める（パッケージ・層構成）</t>
   </si>
   <si>
     <t>7</t>
   </si>
   <si>
-    <t>STEP4_テスト戦略</t>
+    <t>STEP4_設計書作成</t>
+  </si>
+  <si>
+    <t>基本設計書・詳細設計書として何を書くか決める</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>STEP5_本番リリース・インフラ構成</t>
+  </si>
+  <si>
+    <t>サーバー構成・AWS対応可否・バッチ処理をどう構築するか決める</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>STEP6_テスト戦略</t>
   </si>
   <si>
     <t>どう確認するか決める</t>
   </si>
   <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>STEP5_着手前チェック</t>
+    <t>10</t>
+  </si>
+  <si>
+    <t>STEP7_着手前チェック</t>
   </si>
   <si>
     <t>着手前の最終確認</t>
   </si>
   <si>
-    <t>全体像：何から考えるべきか（5つのSTEP）</t>
-  </si>
-  <si>
-    <t>プロジェクトを一から作る際、この順番で検討すると手戻りが少ない</t>
+    <t>全体像：何から考えるべきか（7つのSTEP）</t>
+  </si>
+  <si>
+    <t>プロジェクトを一から作る際、この順番で検討すると手戻りが少ない（設計書作成・本番リリースを含む）</t>
   </si>
   <si>
     <t>STEP1</t>
@@ -159,27 +179,40 @@
     <t>STEP5</t>
   </si>
   <si>
+    <t>STEP6</t>
+  </si>
+  <si>
+    <t>STEP7</t>
+  </si>
+  <si>
     <t xml:space="preserve">要件整理
-何を
-作るか
+何を作るか
 整理する</t>
   </si>
   <si>
     <t xml:space="preserve">技術選定
-何を
-使うか
+何を使うか
 決める</t>
   </si>
   <si>
     <t xml:space="preserve">構成設計
-どう
-組み立てるか
+どう組み立てるか
 決める</t>
   </si>
   <si>
+    <t xml:space="preserve">設計書作成
+基本設計書
+詳細設計書を作る</t>
+  </si>
+  <si>
+    <t xml:space="preserve">本番リリース
+インフラ構成
+サーバー・AWS
+バッチを決める</t>
+  </si>
+  <si>
     <t xml:space="preserve">テスト戦略
-どう
-確認するか
+どう確認するか
 決める</t>
   </si>
   <si>
@@ -191,15 +224,19 @@
     <t>■ 各STEPの位置づけ</t>
   </si>
   <si>
-    <t xml:space="preserve">STEP1 要件整理　　　業務フローを洗い出し、機能単位に分解し、守るべき業務ルールを言語化する
+    <t xml:space="preserve">STEP1 要件整理　　　　　　　　業務フローを洗い出し、機能単位に分解し、守るべき業務ルールを言語化する
 　　　　↓
-STEP2 技術選定　　　言語／DB／画面技術／テスト手法など、使う技術を1つずつ検討して決める
+STEP2 技術選定　　　　　　　　言語／DB／画面技術（JavaScript・CSS含む）／IDE／開発手法を決める
 　　　　↓
-STEP3 構成設計　　　パッケージ構成・層構成（entity/repository/service/controller）を決める
+STEP3 構成設計　　　　　　　　パッケージ構成・層構成（entity/repository/service/controller）を決める
 　　　　↓
-STEP4 テスト戦略　　テスト用DBの分離、テストの粒度、異常系の観点を最初から組み込む
+STEP4 設計書作成　　　　　　　基本設計書（画面・DB・I/F）と詳細設計書（クラス・処理フロー・バッチ）を作る
 　　　　↓
-STEP5 着手前チェック　ここまでの検討内容を10項目のチェックリストで最終確認してから着手する
+STEP5 本番リリース・インフラ構成　サーバー構成（Web／AP／DB）、AWS向けかどうか、バッチ処理の運用方式を決める
+　　　　↓
+STEP6 テスト戦略　　　　　　　テスト用DBの分離、テストの粒度、異常系の観点を最初から組み込む
+　　　　↓
+STEP7 着手前チェック　　　　　ここまでの検討内容をチェックリストで最終確認してから着手する
 ※ 実際には行き来しながら詰めることも多いが、「最初にどの順番で考えるか」の目安として使う。</t>
   </si>
   <si>
@@ -234,7 +271,7 @@
     <t>STEP2　技術選定　－　何を使うか決める</t>
   </si>
   <si>
-    <t>💡 このSTEPで問うこと： 言語・DB・画面技術・テスト手法として、何を選ぶか？その理由は？</t>
+    <t>💡 このSTEPで問うこと： 言語・DB・画面技術（JS/CSS含む）・IDE・開発手法として、何を選ぶか？その理由は？</t>
   </si>
   <si>
     <t>分類</t>
@@ -252,7 +289,7 @@
     <t>言語／FW</t>
   </si>
   <si>
-    <t>Java+Spring Boot 等</t>
+    <t>Java＋Spring Boot 等</t>
   </si>
   <si>
     <t>採用実績・学習コスト・標準機能</t>
@@ -261,10 +298,10 @@
     <t>DB（本番）</t>
   </si>
   <si>
-    <t>PostgreSQL／MySQL 等</t>
-  </si>
-  <si>
-    <t>コスト・案件実績・必要機能</t>
+    <t>PostgreSQL／MySQL／Oracle 等</t>
+  </si>
+  <si>
+    <t>コスト・案件実績・必要機能・ライセンス条件</t>
   </si>
   <si>
     <t>DB（テスト）</t>
@@ -276,38 +313,75 @@
     <t>テスト速度・環境構築の手間</t>
   </si>
   <si>
-    <t>画面技術</t>
-  </si>
-  <si>
-    <t>Thymeleaf／SPA 等</t>
+    <t>画面技術（HTML側）</t>
+  </si>
+  <si>
+    <t>Thymeleaf（SSR）／SPA（React/Vue等）</t>
   </si>
   <si>
     <t>開発環境の手間・対話性の必要度</t>
   </si>
   <si>
+    <t>画面の動的処理（JavaScript）</t>
+  </si>
+  <si>
+    <t>素のJavaScript／jQuery／Vue.js 等</t>
+  </si>
+  <si>
+    <t>必要な操作の複雑さ・保守のしやすさ</t>
+  </si>
+  <si>
+    <t>デザイン（CSS）</t>
+  </si>
+  <si>
+    <t>CSS／Bootstrap／Tailwind 等</t>
+  </si>
+  <si>
+    <t>見た目の作り込み度合い・部品の再利用性</t>
+  </si>
+  <si>
     <t>スキーマ管理</t>
   </si>
   <si>
-    <t>Flyway等／自動生成</t>
-  </si>
-  <si>
-    <t>変更履歴・本番事故リスク</t>
+    <t>Flyway等のマイグレーション／自動生成</t>
+  </si>
+  <si>
+    <t>変更履歴の残し方・本番事故リスク</t>
   </si>
   <si>
     <t>テスト・カバレッジ</t>
   </si>
   <si>
-    <t>JUnit+MockMvc／JaCoCo等</t>
+    <t>JUnit＋MockMvc／JaCoCo等</t>
   </si>
   <si>
     <t>品質担保レベル・運用の手間</t>
   </si>
   <si>
+    <t>IDE</t>
+  </si>
+  <si>
+    <t>Eclipse／IntelliJ IDEA／VS Code 等</t>
+  </si>
+  <si>
+    <t>チームでの統一のしやすさ・プラグインの充実度</t>
+  </si>
+  <si>
+    <t>開発手法</t>
+  </si>
+  <si>
+    <t>ウォーターフォール／アジャイル 等</t>
+  </si>
+  <si>
+    <t>案件特性（要件の確定度合い）・チーム規模</t>
+  </si>
+  <si>
     <t>ポイント</t>
   </si>
   <si>
     <t xml:space="preserve">・「流行っているから」ではなく、案件・チームでの実績や学習コストとの見合いで選ぶ
-・本番用とテスト用でDBを分ける等、後から変更しづらい選択は最初に決めておく</t>
+・本番用とテスト用でDBを分ける等、後から変更しづらい選択は最初に決めておく
+・案件によってIDE・開発手法・DB（Oracle指定等）があらかじめ決まっていることも多いので、まず案件の制約を確認する</t>
   </si>
   <si>
     <t>STEP3　構成設計　－　どう組み立てるか決める</t>
@@ -367,7 +441,134 @@
 ・画面入力用（Form/DTO）とDB用（Entity）を分けるかどうかも、この段階で決めておく</t>
   </si>
   <si>
-    <t>STEP4　テスト戦略　－　どう確認するか決める</t>
+    <t>STEP4　設計書作成　－　基本設計書・詳細設計書を作る</t>
+  </si>
+  <si>
+    <t>💡 このSTEPで問うこと： 基本設計書・詳細設計書として、何を・どこまで書くか？</t>
+  </si>
+  <si>
+    <t>① 基本設計書（外部設計）に書くこと</t>
+  </si>
+  <si>
+    <t xml:space="preserve">・画面設計：画面遷移図、画面レイアウト、入出力項目定義書
+・DB設計：ER図、テーブル定義書
+・外部インターフェース設計：他システム連携仕様、API仕様
+・バッチ処理の概要：どんなバッチが必要か、処理タイミングの方針</t>
+  </si>
+  <si>
+    <t>② 詳細設計書（内部設計）に書くこと</t>
+  </si>
+  <si>
+    <t xml:space="preserve">・クラス設計：クラス図、各クラスの責務
+・処理フロー：シーケンス図、フローチャート
+・SQL設計：発行するSQL、性能を意識したインデックス設計
+・バッチの詳細処理：起動契機、リトライ方針、ログ出力仕様
+・例外設計：エラーコード、エラーメッセージ、異常時の挙動</t>
+  </si>
+  <si>
+    <t xml:space="preserve">・STEP1で言語化した業務ルールを、基本設計のI/F定義・詳細設計の例外設計にそのまま反映する
+・ウォーターフォール型開発ではこの設計書がレビュー対象となるため、実装前に関係者の合意を取っておく</t>
+  </si>
+  <si>
+    <t>STEP5　本番リリース・インフラ構成　－　サーバー・AWS対応・バッチを決める</t>
+  </si>
+  <si>
+    <t>💡 このSTEPで問うこと： 本番環境はどこに、どんな構成で構築するか？バッチ処理はどう動かすか？</t>
+  </si>
+  <si>
+    <t>■ ①インフラ方式（AWSなどクラウド向け／AWS向けでない場合）</t>
+  </si>
+  <si>
+    <t>方式</t>
+  </si>
+  <si>
+    <t>選んだ方式と理由（記入欄）</t>
+  </si>
+  <si>
+    <t>AWSなどクラウド向け</t>
+  </si>
+  <si>
+    <t>EC2/ECS/Fargate等でアプリ実行、RDSでDB、S3でファイル保管、ALBで負荷分散、CloudWatchで監視</t>
+  </si>
+  <si>
+    <t>スケーラビリティ、初期コストを抑えたいか、運用の自動化度合い</t>
+  </si>
+  <si>
+    <t>AWS向けでない（オンプレミス／社内サーバ）</t>
+  </si>
+  <si>
+    <t>自社所有・データセンターのサーバにミドルウェアを直接構築・運用</t>
+  </si>
+  <si>
+    <t>既存の社内インフラとの親和性、セキュリティポリシー、長期利用コスト</t>
+  </si>
+  <si>
+    <t>■ ②サーバー構成</t>
+  </si>
+  <si>
+    <t>サーバー種別</t>
+  </si>
+  <si>
+    <t>選んだもの（記入欄）</t>
+  </si>
+  <si>
+    <t>Webサーバー</t>
+  </si>
+  <si>
+    <t>Nginx／Apache HTTPD 等</t>
+  </si>
+  <si>
+    <t>静的ファイル配信・リバースプロキシの要否</t>
+  </si>
+  <si>
+    <t>APサーバー</t>
+  </si>
+  <si>
+    <t>組み込みTomcat／外部Tomcat／WildFly／WebLogic 等</t>
+  </si>
+  <si>
+    <t>案件の標準構成、可用性要件</t>
+  </si>
+  <si>
+    <t>DBサーバー</t>
+  </si>
+  <si>
+    <t>Oracle／PostgreSQL／MySQL 等</t>
+  </si>
+  <si>
+    <t>案件で指定されたDB、ライセンスコスト</t>
+  </si>
+  <si>
+    <t>■ ③バッチ処理の設計</t>
+  </si>
+  <si>
+    <t>検討項目</t>
+  </si>
+  <si>
+    <t>実行方式</t>
+  </si>
+  <si>
+    <t>Spring Batch／cron＋シェルスクリプト／ジョブ管理ツール（JP1等）</t>
+  </si>
+  <si>
+    <t>起動契機</t>
+  </si>
+  <si>
+    <t>定時実行／手動実行／イベント契機（ファイル到着等）</t>
+  </si>
+  <si>
+    <t>異常時の運用</t>
+  </si>
+  <si>
+    <t>リトライ回数、通知先（メール／監視ツール）、ログ出力ルール</t>
+  </si>
+  <si>
+    <t xml:space="preserve">・案件によってAWS前提かオンプレ前提かは決まっていることが多いため、まず案件の制約を確認する
+・バッチ処理は画面と違い動作が目に見えないため、ログ・監視・異常時の運用設計を特に丁寧に行う
+・環境（開発／本番）ごとにDB接続情報等を切り替えられる設定にしておく（環境変数化）</t>
+  </si>
+  <si>
+    <t>STEP6　テスト戦略　－　どう確認するか決める</t>
   </si>
   <si>
     <t>💡 このSTEPで問うこと： テストはどの粒度で、どこまで自動化しておくか？</t>
@@ -400,10 +601,10 @@
 ・カバレッジ計測とワンクリック実行の仕組みを、開発の早い段階で用意する</t>
   </si>
   <si>
-    <t>STEP5　着手前チェック　－　最終確認をする</t>
-  </si>
-  <si>
-    <t>💡 このSTEPで問うこと： STEP1〜4で決めたことに、抜け漏れはないか？</t>
+    <t>STEP7　着手前チェック　－　最終確認をする</t>
+  </si>
+  <si>
+    <t>💡 このSTEPで問うこと： STEP1〜6で決めたことに、抜け漏れはないか？</t>
   </si>
   <si>
     <t>順番</t>
@@ -469,29 +670,41 @@
     <t>業務ロジック層は単体、画面/API層は統合、と役割分担を決める</t>
   </si>
   <si>
-    <t>9</t>
-  </si>
-  <si>
     <t>カバレッジ計測・ワンクリック実行を早めに組み込む</t>
   </si>
   <si>
     <t>導入と、非エンジニアでも実行できるスクリプトの用意を後回しにしない</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
     <t>ドキュメント化の方針を決める</t>
   </si>
   <si>
     <t>自分用メモか非エンジニア向け手順書かで書き方・粒度を変える</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>基本設計書・詳細設計書のレビューを受ける</t>
+  </si>
+  <si>
+    <t>実装に入る前に、関係者（上長・チームメンバー）の合意を得ておく</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>本番のサーバー構成・バッチ運用方針を確認する</t>
+  </si>
+  <si>
+    <t>AWS向けかオンプレか、バッチの監視・異常時対応方法を明確にしてから着手する</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -550,12 +763,6 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF2F4A66"/>
-      <sz val="11"/>
-      <name val="Yu Gothic"/>
-    </font>
-    <font>
-      <b/>
       <color rgb="FF3E5E82"/>
       <sz val="12"/>
       <name val="Yu Gothic"/>
@@ -579,7 +786,7 @@
       <name val="Yu Gothic"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -609,11 +816,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFCEFD0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -674,13 +876,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -713,28 +915,27 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1104,7 +1305,7 @@
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
     </row>
-    <row r="11" ht="26" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="11" ht="30" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
         <v>1</v>
       </c>
@@ -1112,7 +1313,7 @@
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
     </row>
-    <row r="15" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>2</v>
       </c>
@@ -1170,13 +1371,274 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="8" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
+    <col min="4" max="4" width="44" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="40" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+    </row>
+    <row r="3" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+    </row>
+    <row r="5" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="6" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="12" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="13" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="14" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="15" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="16" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="17" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>184</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A3:E3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="45" customWidth="1"/>
+    <col min="2" max="2" width="48" customWidth="1"/>
     <col min="3" max="3" width="55" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1291,6 +1753,28 @@
       </c>
       <c r="C12" s="11" t="s">
         <v>37</v>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1305,24 +1789,28 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="4" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="4" customWidth="1"/>
-    <col min="6" max="6" width="20" customWidth="1"/>
-    <col min="7" max="7" width="4" customWidth="1"/>
-    <col min="8" max="8" width="20" customWidth="1"/>
-    <col min="9" max="9" width="4" customWidth="1"/>
-    <col min="10" max="10" width="20" customWidth="1"/>
+    <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="3" max="3" width="3" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="5" max="5" width="3" customWidth="1"/>
+    <col min="6" max="6" width="17" customWidth="1"/>
+    <col min="7" max="7" width="3" customWidth="1"/>
+    <col min="8" max="8" width="17" customWidth="1"/>
+    <col min="9" max="9" width="3" customWidth="1"/>
+    <col min="10" max="10" width="17" customWidth="1"/>
+    <col min="11" max="11" width="3" customWidth="1"/>
+    <col min="12" max="12" width="17" customWidth="1"/>
+    <col min="13" max="13" width="3" customWidth="1"/>
+    <col min="14" max="14" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" ht="32" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -1333,10 +1821,14 @@
       <c r="H1" s="5"/>
       <c r="I1" s="5"/>
       <c r="J1" s="5"/>
-    </row>
-    <row r="2" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+    </row>
+    <row r="2" ht="22" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -1347,97 +1839,124 @@
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
       <c r="J2" s="6"/>
-    </row>
-    <row r="4" ht="26" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+    </row>
+    <row r="4" ht="26" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B4" s="12" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="5" ht="26" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+      <c r="K4" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="L4" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="M4" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="N4" s="12" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B5" s="14" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" ht="26" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+      <c r="L5" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="N5" s="14" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B6" s="14"/>
       <c r="D6" s="14"/>
       <c r="F6" s="14"/>
       <c r="H6" s="14"/>
       <c r="J6" s="14"/>
-    </row>
-    <row r="7" ht="26" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="L6" s="14"/>
+      <c r="N6" s="14"/>
+    </row>
+    <row r="7" ht="22" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B7" s="14"/>
       <c r="D7" s="14"/>
       <c r="F7" s="14"/>
       <c r="H7" s="14"/>
       <c r="J7" s="14"/>
-    </row>
-    <row r="9" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="15"/>
-      <c r="J9" s="15"/>
-    </row>
-    <row r="10" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="B10" s="16"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="16"/>
-      <c r="I10" s="16"/>
-      <c r="J10" s="16"/>
-    </row>
-    <row r="11" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="16"/>
+      <c r="L7" s="14"/>
+      <c r="N7" s="14"/>
+    </row>
+    <row r="8" ht="22" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="L8" s="14"/>
+      <c r="N8" s="14"/>
+    </row>
+    <row r="10" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10" s="15"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="15"/>
+      <c r="N10" s="15"/>
+    </row>
+    <row r="11" ht="22" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="16" t="s">
+        <v>62</v>
+      </c>
       <c r="B11" s="16"/>
       <c r="C11" s="16"/>
       <c r="D11" s="16"/>
@@ -1447,8 +1966,12 @@
       <c r="H11" s="16"/>
       <c r="I11" s="16"/>
       <c r="J11" s="16"/>
-    </row>
-    <row r="12" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K11" s="16"/>
+      <c r="L11" s="16"/>
+      <c r="M11" s="16"/>
+      <c r="N11" s="16"/>
+    </row>
+    <row r="12" ht="22" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="16"/>
       <c r="B12" s="16"/>
       <c r="C12" s="16"/>
@@ -1459,8 +1982,12 @@
       <c r="H12" s="16"/>
       <c r="I12" s="16"/>
       <c r="J12" s="16"/>
-    </row>
-    <row r="13" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K12" s="16"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="16"/>
+      <c r="N12" s="16"/>
+    </row>
+    <row r="13" ht="22" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="16"/>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
@@ -1471,8 +1998,12 @@
       <c r="H13" s="16"/>
       <c r="I13" s="16"/>
       <c r="J13" s="16"/>
-    </row>
-    <row r="14" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K13" s="16"/>
+      <c r="L13" s="16"/>
+      <c r="M13" s="16"/>
+      <c r="N13" s="16"/>
+    </row>
+    <row r="14" ht="22" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="16"/>
       <c r="B14" s="16"/>
       <c r="C14" s="16"/>
@@ -1483,8 +2014,12 @@
       <c r="H14" s="16"/>
       <c r="I14" s="16"/>
       <c r="J14" s="16"/>
-    </row>
-    <row r="15" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K14" s="16"/>
+      <c r="L14" s="16"/>
+      <c r="M14" s="16"/>
+      <c r="N14" s="16"/>
+    </row>
+    <row r="15" ht="22" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="16"/>
       <c r="B15" s="16"/>
       <c r="C15" s="16"/>
@@ -1495,18 +2030,72 @@
       <c r="H15" s="16"/>
       <c r="I15" s="16"/>
       <c r="J15" s="16"/>
+      <c r="K15" s="16"/>
+      <c r="L15" s="16"/>
+      <c r="M15" s="16"/>
+      <c r="N15" s="16"/>
+    </row>
+    <row r="16" ht="22" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="16"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="16"/>
+      <c r="K16" s="16"/>
+      <c r="L16" s="16"/>
+      <c r="M16" s="16"/>
+      <c r="N16" s="16"/>
+    </row>
+    <row r="17" ht="22" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="16"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="16"/>
+      <c r="J17" s="16"/>
+      <c r="K17" s="16"/>
+      <c r="L17" s="16"/>
+      <c r="M17" s="16"/>
+      <c r="N17" s="16"/>
+    </row>
+    <row r="18" ht="22" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" s="16"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="16"/>
+      <c r="J18" s="16"/>
+      <c r="K18" s="16"/>
+      <c r="L18" s="16"/>
+      <c r="M18" s="16"/>
+      <c r="N18" s="16"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="D5:D7"/>
-    <mergeCell ref="F5:F7"/>
-    <mergeCell ref="H5:H7"/>
-    <mergeCell ref="J5:J7"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="A10:J15"/>
+  <mergeCells count="11">
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="B5:B8"/>
+    <mergeCell ref="D5:D8"/>
+    <mergeCell ref="F5:F8"/>
+    <mergeCell ref="H5:H8"/>
+    <mergeCell ref="J5:J8"/>
+    <mergeCell ref="L5:L8"/>
+    <mergeCell ref="N5:N8"/>
+    <mergeCell ref="A10:N10"/>
+    <mergeCell ref="A11:N18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -1525,56 +2114,56 @@
   <sheetData>
     <row r="1" ht="40" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
     </row>
     <row r="3" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="B3" s="18"/>
       <c r="C3" s="18"/>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="19" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="B5" s="19"/>
       <c r="C5" s="19"/>
     </row>
     <row r="6" ht="90" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="20" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="B6" s="20"/>
       <c r="C6" s="20"/>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="B8" s="19"/>
       <c r="C8" s="19"/>
     </row>
     <row r="9" ht="45" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="20" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="B9" s="20"/>
       <c r="C9" s="20"/>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="B11" s="15"/>
       <c r="C11" s="15"/>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="21" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="B12" s="21"/>
       <c r="C12" s="21"/>
@@ -1622,7 +2211,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1633,7 +2222,7 @@
   <sheetData>
     <row r="1" ht="40" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -1641,7 +2230,7 @@
     </row>
     <row r="3" ht="36" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="B3" s="18"/>
       <c r="C3" s="18"/>
@@ -1649,124 +2238,180 @@
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="6" ht="42" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" ht="42" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" ht="40" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" ht="42" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" ht="40" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9" ht="42" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" ht="40" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" ht="42" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" ht="42" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11" ht="40" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-    </row>
-    <row r="14" ht="45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="20" t="s">
-        <v>86</v>
-      </c>
-      <c r="B14" s="20"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" ht="40" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" ht="40" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" ht="40" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" ht="40" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+    </row>
+    <row r="18" ht="60" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A18:D18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -1785,108 +2430,108 @@
   <sheetData>
     <row r="1" ht="40" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
     </row>
     <row r="3" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="B3" s="18"/>
       <c r="C3" s="18"/>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="19" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="B5" s="19"/>
       <c r="C5" s="19"/>
     </row>
     <row r="6" ht="65" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="20" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="B6" s="20"/>
       <c r="C6" s="20"/>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="B15" s="19"/>
       <c r="C15" s="19"/>
     </row>
     <row r="16" ht="45" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="20" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="B16" s="20"/>
       <c r="C16" s="20"/>
@@ -1907,6 +2552,445 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B20"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="68" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="40" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="B1" s="17"/>
+    </row>
+    <row r="3" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="B3" s="18"/>
+    </row>
+    <row r="5" ht="18" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="B5" s="19"/>
+    </row>
+    <row r="6" ht="85" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="B6" s="20"/>
+    </row>
+    <row r="8" ht="18" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="B8" s="19"/>
+    </row>
+    <row r="9" ht="100" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="B9" s="20"/>
+    </row>
+    <row r="11" ht="18" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="B11" s="19"/>
+    </row>
+    <row r="12" ht="45" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="B12" s="20"/>
+    </row>
+    <row r="14" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="B14" s="15"/>
+    </row>
+    <row r="15" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B15" s="21"/>
+    </row>
+    <row r="16" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="21"/>
+      <c r="B16" s="21"/>
+    </row>
+    <row r="17" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="21"/>
+      <c r="B17" s="21"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="21"/>
+      <c r="B18" s="21"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="21"/>
+      <c r="B19" s="21"/>
+    </row>
+    <row r="20" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="21"/>
+      <c r="B20" s="21"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B20"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="38" customWidth="1"/>
+    <col min="4" max="4" width="30" customWidth="1"/>
+    <col min="5" max="5" width="26" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="40" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+    </row>
+    <row r="3" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+    </row>
+    <row r="5" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+    </row>
+    <row r="6" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" ht="65" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" ht="65" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="B10" s="15"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+    </row>
+    <row r="11" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" ht="40" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" ht="40" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" ht="40" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+    </row>
+    <row r="17" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="18" ht="40" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="19" ht="40" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" ht="40" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="19"/>
+    </row>
+    <row r="23" ht="65" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="B23" s="20"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+    </row>
+    <row r="25" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="B25" s="15"/>
+      <c r="C25" s="15"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
+    </row>
+    <row r="26" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B26" s="21"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
+    </row>
+    <row r="27" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="21"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="21"/>
+    </row>
+    <row r="28" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="21"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="21"/>
+      <c r="B29" s="21"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="21"/>
+    </row>
+    <row r="30" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="21"/>
+      <c r="B30" s="21"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="21"/>
+    </row>
+    <row r="31" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="21"/>
+      <c r="B31" s="21"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="21"/>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A26:E31"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
@@ -1917,61 +3001,61 @@
   <sheetData>
     <row r="1" ht="40" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>105</v>
+        <v>166</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
     </row>
     <row r="3" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
-        <v>106</v>
+        <v>167</v>
       </c>
       <c r="B3" s="18"/>
       <c r="C3" s="18"/>
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>107</v>
+        <v>168</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>108</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>109</v>
+        <v>170</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>110</v>
+        <v>171</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>111</v>
+        <v>172</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>112</v>
+        <v>173</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
-        <v>113</v>
+        <v>174</v>
       </c>
       <c r="B9" s="19"/>
       <c r="C9" s="19"/>
     </row>
     <row r="10" ht="85" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="20" t="s">
-        <v>114</v>
+        <v>175</v>
       </c>
       <c r="B10" s="20"/>
       <c r="C10" s="20"/>
@@ -1986,231 +3070,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E15"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="8" customWidth="1"/>
-    <col min="3" max="3" width="34" customWidth="1"/>
-    <col min="4" max="4" width="44" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
-        <v>115</v>
-      </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-    </row>
-    <row r="3" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-    </row>
-    <row r="5" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="6" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="7" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="8" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="9" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="10" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="11" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="12" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="13" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="14" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="15" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>123</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A3:E3"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
 </file>
--- a/docs/技術選定・構成検討テンプレート（汎用）.xlsx
+++ b/docs/技術選定・構成検討テンプレート（汎用）.xlsx
@@ -11,16 +11,17 @@
     <sheet sheetId="5" name="STEP2_技術選定" state="visible" r:id="rId8"/>
     <sheet sheetId="6" name="STEP3_構成設計" state="visible" r:id="rId9"/>
     <sheet sheetId="7" name="STEP4_設計書作成" state="visible" r:id="rId10"/>
-    <sheet sheetId="8" name="STEP5_本番リリース・インフラ構成" state="visible" r:id="rId11"/>
-    <sheet sheetId="9" name="STEP6_テスト戦略" state="visible" r:id="rId12"/>
-    <sheet sheetId="10" name="STEP7_着手前チェック" state="visible" r:id="rId13"/>
+    <sheet sheetId="8" name="STEP5①_インフラ・サーバー構成" state="visible" r:id="rId11"/>
+    <sheet sheetId="9" name="STEP5②_バッチ処理設計" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="STEP6_テスト戦略" state="visible" r:id="rId13"/>
+    <sheet sheetId="11" name="STEP7_着手前チェック" state="visible" r:id="rId14"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="214">
   <si>
     <t xml:space="preserve">Spring Bootプロジェクト
 技術選定・構成検討テンプレート</t>
@@ -131,22 +132,31 @@
     <t>8</t>
   </si>
   <si>
-    <t>STEP5_本番リリース・インフラ構成</t>
-  </si>
-  <si>
-    <t>サーバー構成・AWS対応可否・バッチ処理をどう構築するか決める</t>
+    <t>STEP5①_インフラ・サーバー構成</t>
+  </si>
+  <si>
+    <t>サーバー構成・AWS対応可否をどう構築するか決める</t>
   </si>
   <si>
     <t>9</t>
   </si>
   <si>
+    <t>STEP5②_バッチ処理設計</t>
+  </si>
+  <si>
+    <t>バッチ処理の実行方式・運用をどう決めるか</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
     <t>STEP6_テスト戦略</t>
   </si>
   <si>
     <t>どう確認するか決める</t>
   </si>
   <si>
-    <t>10</t>
+    <t>11</t>
   </si>
   <si>
     <t>STEP7_着手前チェック</t>
@@ -232,7 +242,7 @@
 　　　　↓
 STEP4 設計書作成　　　　　　　基本設計書（画面・DB・I/F）と詳細設計書（クラス・処理フロー・バッチ）を作る
 　　　　↓
-STEP5 本番リリース・インフラ構成　サーバー構成（Web／AP／DB）、AWS向けかどうか、バッチ処理の運用方式を決める
+STEP5 本番リリース・インフラ構成　①サーバー構成（Web／AP／DB）・AWS向けかどうか　②バッチ処理の運用方式を決める
 　　　　↓
 STEP6 テスト戦略　　　　　　　テスト用DBの分離、テストの粒度、異常系の観点を最初から組み込む
 　　　　↓
@@ -470,10 +480,10 @@
 ・ウォーターフォール型開発ではこの設計書がレビュー対象となるため、実装前に関係者の合意を取っておく</t>
   </si>
   <si>
-    <t>STEP5　本番リリース・インフラ構成　－　サーバー・AWS対応・バッチを決める</t>
-  </si>
-  <si>
-    <t>💡 このSTEPで問うこと： 本番環境はどこに、どんな構成で構築するか？バッチ処理はどう動かすか？</t>
+    <t>STEP5①　本番リリース・インフラ構成（サーバー構成）－ AWS対応を決める</t>
+  </si>
+  <si>
+    <t>💡 このSTEPで問うこと： 本番環境はどこに、どんなサーバー構成で構築するか？</t>
   </si>
   <si>
     <t>■ ①インフラ方式（AWSなどクラウド向け／AWS向けでない場合）</t>
@@ -539,7 +549,18 @@
     <t>案件で指定されたDB、ライセンスコスト</t>
   </si>
   <si>
-    <t>■ ③バッチ処理の設計</t>
+    <t xml:space="preserve">・案件によってAWS前提かオンプレ前提かは決まっていることが多いため、まず案件の制約を確認する
+・環境（開発／本番）ごとにDB接続情報等を切り替えられる設定にしておく（環境変数化）
+・AWSサービスの詳細（EC2/ECS/RDS等の使い分けや典型構成）は「AWS構成検討まとめ.xlsx」を参照</t>
+  </si>
+  <si>
+    <t>STEP5②　本番リリース・インフラ構成（バッチ処理）－ 運用方式を決める</t>
+  </si>
+  <si>
+    <t>💡 このSTEPで問うこと： バッチ処理はどう動かし、どう運用するか？</t>
+  </si>
+  <si>
+    <t>■ バッチ処理の設計</t>
   </si>
   <si>
     <t>検討項目</t>
@@ -563,9 +584,8 @@
     <t>リトライ回数、通知先（メール／監視ツール）、ログ出力ルール</t>
   </si>
   <si>
-    <t xml:space="preserve">・案件によってAWS前提かオンプレ前提かは決まっていることが多いため、まず案件の制約を確認する
-・バッチ処理は画面と違い動作が目に見えないため、ログ・監視・異常時の運用設計を特に丁寧に行う
-・環境（開発／本番）ごとにDB接続情報等を切り替えられる設定にしておく（環境変数化）</t>
+    <t xml:space="preserve">・バッチ処理は画面と違い動作が目に見えないため、ログ・監視・異常時の運用設計を特に丁寧に行う
+・「起動したはずが動いていなかった」を防ぐため、正常終了・異常終了をどう検知するかを先に決める</t>
   </si>
   <si>
     <t>STEP6　テスト戦略　－　どう確認するか決める</t>
@@ -604,7 +624,7 @@
     <t>STEP7　着手前チェック　－　最終確認をする</t>
   </si>
   <si>
-    <t>💡 このSTEPで問うこと： STEP1〜6で決めたことに、抜け漏れはないか？</t>
+    <t>💡 このSTEPで問うこと： ここまでのSTEPで決めたことに、抜け漏れはないか？</t>
   </si>
   <si>
     <t>順番</t>
@@ -680,9 +700,6 @@
   </si>
   <si>
     <t>自分用メモか非エンジニア向け手順書かで書き方・粒度を変える</t>
-  </si>
-  <si>
-    <t>11</t>
   </si>
   <si>
     <t>基本設計書・詳細設計書のレビューを受ける</t>
@@ -1373,6 +1390,89 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="64" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="40" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="17" t="s">
+        <v>172</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+    </row>
+    <row r="3" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="18" t="s">
+        <v>173</v>
+      </c>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+    </row>
+    <row r="5" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="19" t="s">
+        <v>180</v>
+      </c>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+    </row>
+    <row r="10" ht="85" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A10:C10"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
@@ -1385,7 +1485,7 @@
   <sheetData>
     <row r="1" ht="40" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -1394,7 +1494,7 @@
     </row>
     <row r="3" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="B3" s="18"/>
       <c r="C3" s="18"/>
@@ -1403,223 +1503,223 @@
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="21" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>15</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="21" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>18</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
     </row>
     <row r="8" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="21" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>20</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
     </row>
     <row r="9" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="21" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>23</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="D9" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="E9" s="10" t="s">
         <v>190</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="10" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="21" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>26</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
     </row>
     <row r="11" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="21" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B11" s="10" t="s">
         <v>29</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="21" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>32</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
     </row>
     <row r="13" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="21" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B13" s="10" t="s">
         <v>35</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
     </row>
     <row r="14" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="21" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>38</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
     </row>
     <row r="15" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="21" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B15" s="10" t="s">
         <v>41</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
     </row>
     <row r="16" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="21" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>203</v>
+        <v>44</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
     </row>
     <row r="17" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="21" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -1634,7 +1734,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1775,6 +1875,17 @@
       </c>
       <c r="C14" s="11" t="s">
         <v>43</v>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -1810,7 +1921,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -1828,7 +1939,7 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -1846,66 +1957,66 @@
     </row>
     <row r="4" ht="26" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B4" s="12" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H4" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="I4" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="I4" s="13" t="s">
-        <v>47</v>
-      </c>
       <c r="J4" s="12" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K4" s="13" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="L4" s="12" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="M4" s="13" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="N4" s="12" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B5" s="14" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="L5" s="14" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N5" s="14" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
@@ -1937,7 +2048,7 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B10" s="15"/>
       <c r="C10" s="15"/>
@@ -1955,7 +2066,7 @@
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B11" s="16"/>
       <c r="C11" s="16"/>
@@ -2114,56 +2225,56 @@
   <sheetData>
     <row r="1" ht="40" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
     </row>
     <row r="3" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B3" s="18"/>
       <c r="C3" s="18"/>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="19" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B5" s="19"/>
       <c r="C5" s="19"/>
     </row>
     <row r="6" ht="90" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="20" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B6" s="20"/>
       <c r="C6" s="20"/>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B8" s="19"/>
       <c r="C8" s="19"/>
     </row>
     <row r="9" ht="45" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="20" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B9" s="20"/>
       <c r="C9" s="20"/>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B11" s="15"/>
       <c r="C11" s="15"/>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="21" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B12" s="21"/>
       <c r="C12" s="21"/>
@@ -2222,7 +2333,7 @@
   <sheetData>
     <row r="1" ht="40" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -2230,7 +2341,7 @@
     </row>
     <row r="3" ht="36" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B3" s="18"/>
       <c r="C3" s="18"/>
@@ -2238,161 +2349,161 @@
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" ht="40" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" ht="40" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" ht="40" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" ht="40" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10" ht="40" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11" ht="40" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12" ht="40" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" ht="40" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14" ht="40" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" ht="40" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="19" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B17" s="19"/>
       <c r="C17" s="19"/>
@@ -2400,7 +2511,7 @@
     </row>
     <row r="18" ht="60" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="20" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B18" s="20"/>
       <c r="C18" s="20"/>
@@ -2430,108 +2541,108 @@
   <sheetData>
     <row r="1" ht="40" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
     </row>
     <row r="3" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B3" s="18"/>
       <c r="C3" s="18"/>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="19" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B5" s="19"/>
       <c r="C5" s="19"/>
     </row>
     <row r="6" ht="65" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="20" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B6" s="20"/>
       <c r="C6" s="20"/>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B15" s="19"/>
       <c r="C15" s="19"/>
     </row>
     <row r="16" ht="45" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="20" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B16" s="20"/>
       <c r="C16" s="20"/>
@@ -2561,61 +2672,61 @@
   <sheetData>
     <row r="1" ht="40" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B1" s="17"/>
     </row>
     <row r="3" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B3" s="18"/>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="19" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B5" s="19"/>
     </row>
     <row r="6" ht="85" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="20" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B6" s="20"/>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B8" s="19"/>
     </row>
     <row r="9" ht="100" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="20" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B9" s="20"/>
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B11" s="19"/>
     </row>
     <row r="12" ht="45" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="20" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B12" s="20"/>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B14" s="15"/>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="21" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B15" s="21"/>
     </row>
@@ -2659,7 +2770,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -2671,7 +2782,7 @@
   <sheetData>
     <row r="1" ht="40" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -2680,7 +2791,7 @@
     </row>
     <row r="3" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B3" s="18"/>
       <c r="C3" s="18"/>
@@ -2689,7 +2800,7 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B5" s="15"/>
       <c r="C5" s="15"/>
@@ -2698,58 +2809,58 @@
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>14</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" ht="65" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" ht="65" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B10" s="15"/>
       <c r="C10" s="15"/>
@@ -2758,231 +2869,153 @@
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12" ht="40" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" ht="40" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14" ht="40" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="16" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-    </row>
-    <row r="17" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="18" ht="40" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="B18" s="11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+    </row>
+    <row r="17" ht="65" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="20" t="s">
         <v>160</v>
       </c>
-      <c r="C18" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="19" ht="40" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="11" t="s">
-        <v>161</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D19" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="20" ht="40" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="19" t="s">
-        <v>107</v>
-      </c>
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
-    </row>
-    <row r="23" ht="65" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="20" t="s">
-        <v>165</v>
-      </c>
-      <c r="B23" s="20"/>
-      <c r="C23" s="20"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="B19" s="15"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
+    </row>
+    <row r="20" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="B20" s="21"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="21"/>
+    </row>
+    <row r="21" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="21"/>
+      <c r="B21" s="21"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="21"/>
+    </row>
+    <row r="22" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="21"/>
+      <c r="B22" s="21"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
+    </row>
+    <row r="23" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="21"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="21"/>
+      <c r="B24" s="21"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
     </row>
     <row r="25" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="B25" s="15"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-    </row>
-    <row r="26" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="B26" s="21"/>
-      <c r="C26" s="21"/>
-      <c r="D26" s="21"/>
-      <c r="E26" s="21"/>
-    </row>
-    <row r="27" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="21"/>
-      <c r="B27" s="21"/>
-      <c r="C27" s="21"/>
-      <c r="D27" s="21"/>
-      <c r="E27" s="21"/>
-    </row>
-    <row r="28" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="21"/>
-      <c r="B28" s="21"/>
-      <c r="C28" s="21"/>
-      <c r="D28" s="21"/>
-      <c r="E28" s="21"/>
-    </row>
-    <row r="29" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="21"/>
-      <c r="B29" s="21"/>
-      <c r="C29" s="21"/>
-      <c r="D29" s="21"/>
-      <c r="E29" s="21"/>
-    </row>
-    <row r="30" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="21"/>
-      <c r="B30" s="21"/>
-      <c r="C30" s="21"/>
-      <c r="D30" s="21"/>
-      <c r="E30" s="21"/>
-    </row>
-    <row r="31" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="21"/>
-      <c r="B31" s="21"/>
-      <c r="C31" s="21"/>
-      <c r="D31" s="21"/>
-      <c r="E31" s="21"/>
+      <c r="A25" s="21"/>
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A10:E10"/>
     <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A26:E31"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A20:E25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -2991,81 +3024,166 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="64" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="55" customWidth="1"/>
+    <col min="4" max="4" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" ht="40" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
-    </row>
-    <row r="3" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" s="17"/>
+    </row>
+    <row r="3" ht="36" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B3" s="18"/>
       <c r="C3" s="18"/>
-    </row>
-    <row r="5" ht="22" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
+      <c r="D3" s="18"/>
+    </row>
+    <row r="5" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+    </row>
+    <row r="6" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7" ht="45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8" ht="45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="B8" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="7" t="s">
+      <c r="C8" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9" ht="45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="11" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="6" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
+      <c r="B9" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="C9" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+    </row>
+    <row r="12" ht="50" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="20" t="s">
         <v>171</v>
       </c>
-      <c r="C6" s="11" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="7" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
-        <v>174</v>
-      </c>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-    </row>
-    <row r="10" ht="85" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="20" t="s">
-        <v>175</v>
-      </c>
-      <c r="B10" s="20"/>
-      <c r="C10" s="20"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+    </row>
+    <row r="14" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+    </row>
+    <row r="15" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="B15" s="21"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+    </row>
+    <row r="16" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="21"/>
+      <c r="B16" s="21"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
+    </row>
+    <row r="17" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="21"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="21"/>
+      <c r="B18" s="21"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="21"/>
+      <c r="B19" s="21"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+    </row>
+    <row r="20" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="21"/>
+      <c r="B20" s="21"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="21"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A10:C10"/>
+  <mergeCells count="7">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A15:D20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
